--- a/artfynd/A 12841-2020 artfynd.xlsx
+++ b/artfynd/A 12841-2020 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 12841-2020 artfynd.xlsx
+++ b/artfynd/A 12841-2020 artfynd.xlsx
@@ -3098,7 +3098,7 @@
         <v>118512952</v>
       </c>
       <c r="B22" t="n">
-        <v>97739</v>
+        <v>97746</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3209,7 +3209,7 @@
         <v>118512951</v>
       </c>
       <c r="B23" t="n">
-        <v>97739</v>
+        <v>97746</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>

--- a/artfynd/A 12841-2020 artfynd.xlsx
+++ b/artfynd/A 12841-2020 artfynd.xlsx
@@ -3095,7 +3095,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>118512952</v>
+        <v>118512951</v>
       </c>
       <c r="B22" t="n">
         <v>97746</v>
@@ -3144,10 +3144,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>726227</v>
+        <v>726223</v>
       </c>
       <c r="R22" t="n">
-        <v>6391381</v>
+        <v>6391269</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3206,7 +3206,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>118512951</v>
+        <v>118512952</v>
       </c>
       <c r="B23" t="n">
         <v>97746</v>
@@ -3255,10 +3255,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>726223</v>
+        <v>726227</v>
       </c>
       <c r="R23" t="n">
-        <v>6391269</v>
+        <v>6391381</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
